--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486902_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486902_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1652</v>
+        <v>4.6429</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9013</v>
+        <v>4.3197</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2639</v>
+        <v>0.3232</v>
       </c>
       <c r="G2" t="n">
         <v>3.7352</v>
@@ -610,13 +610,13 @@
         <v>1.4374</v>
       </c>
       <c r="S2" t="n">
-        <v>1.198</v>
+        <v>1.6757</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8754999999999999</v>
+        <v>1.2939</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3225</v>
+        <v>0.3818</v>
       </c>
       <c r="V2" t="n">
         <v>-1.1786</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5413</v>
+        <v>4.0766</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1423</v>
+        <v>4.3515</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6009</v>
+        <v>-0.2749</v>
       </c>
       <c r="G3" t="n">
         <v>1.6895</v>
@@ -688,13 +688,13 @@
         <v>1.8481</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5931</v>
+        <v>1.1284</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6778</v>
+        <v>0.887</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0847</v>
+        <v>0.2413</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5893</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3652</v>
+        <v>3.4977</v>
       </c>
       <c r="E4" t="n">
-        <v>2.951</v>
+        <v>2.8464</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4142</v>
+        <v>0.6513</v>
       </c>
       <c r="G4" t="n">
         <v>3.5985</v>
@@ -766,13 +766,13 @@
         <v>1.8481</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4525</v>
+        <v>0.585</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6701</v>
+        <v>0.5655</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2176</v>
+        <v>0.0195</v>
       </c>
       <c r="V4" t="n">
         <v>-0.4805</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2095</v>
+        <v>3.4204</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7759</v>
+        <v>1.1943</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4335</v>
+        <v>2.2261</v>
       </c>
       <c r="G5" t="n">
         <v>1.5488</v>
@@ -844,13 +844,13 @@
         <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5785</v>
+        <v>0.7894</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1045</v>
+        <v>0.5229</v>
       </c>
       <c r="U5" t="n">
-        <v>0.474</v>
+        <v>0.2665</v>
       </c>
       <c r="V5" t="n">
         <v>1.2875</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5025</v>
+        <v>1.7423</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0166</v>
+        <v>2.4936</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5142</v>
+        <v>-0.7513</v>
       </c>
       <c r="G6" t="n">
         <v>0.7543</v>
@@ -922,13 +922,13 @@
         <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1588</v>
+        <v>1.3987</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4411</v>
+        <v>0.918</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7178</v>
+        <v>0.4806</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.393</v>
+        <v>1.6015</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4474</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9456</v>
+        <v>0.8864</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3461</v>
@@ -1000,13 +1000,13 @@
         <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9712</v>
+        <v>1.1797</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8944</v>
+        <v>1.1622</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0175</v>
       </c>
       <c r="V7" t="n">
         <v>1.1786</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8147</v>
+        <v>0.1994</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8116</v>
+        <v>-1.753</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6263</v>
+        <v>1.9524</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1808</v>
@@ -1078,13 +1078,13 @@
         <v>1.0267</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9955</v>
+        <v>1.3802</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2043</v>
+        <v>1.2629</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2088</v>
+        <v>0.1173</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0322</v>
+        <v>-0.3092</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8169</v>
+        <v>-3.1081</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7847</v>
+        <v>2.799</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5266</v>
+        <v>-0.9436</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7915</v>
+        <v>-0.6355</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3181</v>
+        <v>-0.3081</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2436</v>
+        <v>-1.6125</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0068</v>
+        <v>-0.8623</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2368</v>
+        <v>-0.7502</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7702</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7846</v>
+        <v>0.2268</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5549</v>
+        <v>0.4422</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.2588</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.1068</v>
+        <v>-2.0534</v>
       </c>
       <c r="R9" t="n">
         <v>1.8481</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5746</v>
+        <v>0.8398</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8677</v>
+        <v>0.5578</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7069</v>
+        <v>0.282</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2099</v>
+        <v>-0.3111</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6442</v>
+        <v>-1.3304</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4343</v>
+        <v>1.0193</v>
       </c>
       <c r="G10" t="n">
         <v>-1.821</v>
@@ -1234,13 +1234,13 @@
         <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6378</v>
+        <v>0.5366</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4534</v>
+        <v>-0.1396</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0912</v>
+        <v>0.6762</v>
       </c>
       <c r="V10" t="n">
         <v>1.1786</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ JIMENEZ</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.145</v>
+        <v>-0.5238</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.014</v>
+        <v>-2.1307</v>
       </c>
       <c r="F11" t="n">
-        <v>0.869</v>
+        <v>1.6068</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5498</v>
+        <v>-0.5266</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3632</v>
+        <v>0.7915</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9131</v>
+        <v>-1.3181</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6579</v>
+        <v>0.2436</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6579</v>
+        <v>0.2368</v>
       </c>
       <c r="M11" t="n">
-        <v>0.108</v>
+        <v>-0.7702</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3632</v>
+        <v>0.7846</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2552</v>
+        <v>-1.5549</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4107</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0267</v>
+        <v>-4.1068</v>
       </c>
       <c r="R11" t="n">
-        <v>0.616</v>
+        <v>1.8481</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1844</v>
+        <v>1.0829</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3294</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1449</v>
+        <v>0.529</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>J. RODRIGUEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4894</v>
+        <v>-0.9218</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2588</v>
+        <v>-1.9094</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7693</v>
+        <v>0.9875</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9436</v>
+        <v>-0.5498</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6355</v>
+        <v>0.3632</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3081</v>
+        <v>-0.9131</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6125</v>
+        <v>-0.6579</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8623</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7502</v>
+        <v>-0.6579</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.108</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2268</v>
+        <v>0.3632</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4422</v>
+        <v>-0.2552</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2053</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8481</v>
+        <v>0.616</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3405</v>
+        <v>0.0387</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5928</v>
+        <v>-0.2248</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2523</v>
+        <v>0.2635</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1426,25 +1426,25 @@
         <v>17.1149</v>
       </c>
       <c r="E13" t="n">
-        <v>5.689000000000003</v>
+        <v>5.689099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>11.4257</v>
+        <v>11.4258</v>
       </c>
       <c r="G13" t="n">
         <v>5.958399999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4213999999999997</v>
+        <v>-0.4213999999999994</v>
       </c>
       <c r="I13" t="n">
         <v>6.379700000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>7.292699999999999</v>
+        <v>7.2927</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.6506</v>
+        <v>-4.650599999999999</v>
       </c>
       <c r="L13" t="n">
         <v>11.9433</v>
@@ -1471,16 +1471,16 @@
         <v>10.6351</v>
       </c>
       <c r="T13" t="n">
-        <v>7.3598</v>
+        <v>7.3597</v>
       </c>
       <c r="U13" t="n">
-        <v>3.2753</v>
+        <v>3.2752</v>
       </c>
       <c r="V13" t="n">
         <v>2.5749</v>
       </c>
       <c r="W13" t="n">
-        <v>8.490499999999999</v>
+        <v>8.490500000000001</v>
       </c>
       <c r="X13" t="n">
         <v>-5.9158</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5752</v>
+        <v>0.8507</v>
       </c>
       <c r="E14" t="n">
-        <v>1.391</v>
+        <v>1.7048</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8158</v>
+        <v>-0.8541</v>
       </c>
       <c r="G14" t="n">
         <v>-0.0772</v>
@@ -1546,13 +1546,13 @@
         <v>2.2588</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3661</v>
+        <v>-1.0907</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1198</v>
+        <v>-0.806</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2463</v>
+        <v>-0.2846</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2402</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. MONTILLA DIAZ</t>
+          <t>J. MOLINA MARTINEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1914</v>
+        <v>0.1293</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2312</v>
+        <v>0.1505</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4225</v>
+        <v>-0.0212</v>
       </c>
       <c r="G15" t="n">
-        <v>0.339</v>
+        <v>0.8468</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7072000000000001</v>
+        <v>2.2833</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3682</v>
+        <v>-1.4365</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3199</v>
+        <v>0.4722</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2015</v>
+        <v>1.0512</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1184</v>
+        <v>-0.579</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0191</v>
+        <v>0.3746</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5057</v>
+        <v>1.2321</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4866</v>
+        <v>-0.8575</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3591</v>
+        <v>-1.3521</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0931</v>
+        <v>-0.3217</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.266</v>
+        <v>-1.0304</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.6366</v>
+        <v>-1.4189</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.4579</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MOLINA MARTINEZ</t>
+          <t>M. MONTILLA DIAZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3658</v>
+        <v>-0.0859</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5818</v>
+        <v>-0.4404</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2159</v>
+        <v>0.3545</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8468</v>
+        <v>0.339</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2833</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4365</v>
+        <v>-0.3682</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4722</v>
+        <v>0.3199</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0512</v>
+        <v>0.2015</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.579</v>
+        <v>0.1184</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3746</v>
+        <v>0.0191</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2321</v>
+        <v>0.5057</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8575</v>
+        <v>-0.4866</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8472</v>
+        <v>-0.6364</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.054</v>
+        <v>-0.3023</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7932</v>
+        <v>-0.334</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4189</v>
+        <v>-1.6366</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.4579</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3962</v>
+        <v>-0.5583</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4023</v>
+        <v>-0.2253</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7986</v>
+        <v>-0.333</v>
       </c>
       <c r="G17" t="n">
         <v>1.3276</v>
@@ -1780,13 +1780,13 @@
         <v>2.4641</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1078</v>
+        <v>-1.2699</v>
       </c>
       <c r="T17" t="n">
-        <v>0.209</v>
+        <v>-0.4186</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.3168</v>
+        <v>-0.8512999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. BELLVER VALIENTE</t>
+          <t>L. FERRANDO ORTELLS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3453</v>
+        <v>-0.9218</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.278</v>
+        <v>0.2514</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9327</v>
+        <v>-1.1732</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1949</v>
+        <v>0.1824</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.824</v>
+        <v>0.477</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3709</v>
+        <v>-0.2947</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.0531</v>
+        <v>1.2891</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.0531</v>
+        <v>0.75</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.5391</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8582</v>
+        <v>-1.1067</v>
       </c>
       <c r="N18" t="n">
-        <v>1.2291</v>
+        <v>-0.2729</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3709</v>
+        <v>-0.8338</v>
       </c>
       <c r="P18" t="n">
         <v>-0.2053</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8214</v>
+        <v>1.8481</v>
       </c>
       <c r="S18" t="n">
-        <v>0.055</v>
+        <v>-0.8988</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8018999999999999</v>
+        <v>-0.1628</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7469</v>
+        <v>-0.736</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. FERRANDO ORTELLS</t>
+          <t>A. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5494</v>
+        <v>-1.9136</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3762</v>
+        <v>-2.9056</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1732</v>
+        <v>0.992</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1824</v>
+        <v>-1.1949</v>
       </c>
       <c r="H19" t="n">
-        <v>0.477</v>
+        <v>-0.824</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2947</v>
+        <v>-0.3709</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2891</v>
+        <v>-2.0531</v>
       </c>
       <c r="K19" t="n">
-        <v>0.75</v>
+        <v>-2.0531</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5391</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1067</v>
+        <v>0.8582</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2729</v>
+        <v>1.2291</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8338</v>
+        <v>-0.3709</v>
       </c>
       <c r="P19" t="n">
         <v>-0.2053</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8481</v>
+        <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5264</v>
+        <v>-0.5134</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7905</v>
+        <v>0.1742</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.736</v>
+        <v>-0.6876</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9717</v>
+        <v>-2.5243</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6908</v>
+        <v>-2.2138</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2809</v>
+        <v>-0.3105</v>
       </c>
       <c r="G20" t="n">
         <v>0.2251</v>
@@ -2014,13 +2014,13 @@
         <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0538</v>
+        <v>-0.4988</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6701</v>
+        <v>0.1471</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6163</v>
+        <v>-0.6459</v>
       </c>
       <c r="V20" t="n">
         <v>0.8295</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6571</v>
+        <v>-2.8778</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4871</v>
+        <v>-2.1732</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1701</v>
+        <v>-0.7045</v>
       </c>
       <c r="G21" t="n">
         <v>-1.976</v>
@@ -2092,13 +2092,13 @@
         <v>1.8481</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.5025</v>
+        <v>-1.7231</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1857</v>
+        <v>-0.8719</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.3168</v>
+        <v>-0.8512999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.794</v>
+        <v>-3.9422</v>
       </c>
       <c r="E22" t="n">
         <v>-3.6317</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1623</v>
+        <v>-0.3105</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4791</v>
@@ -2170,13 +2170,13 @@
         <v>0.616</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-1.0257</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0931</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7844</v>
+        <v>-0.9326</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8019</v>
+        <v>-4.5735</v>
       </c>
       <c r="E23" t="n">
         <v>-2.2915</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5104</v>
+        <v>-2.282</v>
       </c>
       <c r="G23" t="n">
         <v>-4.1518</v>
@@ -2248,13 +2248,13 @@
         <v>2.6694</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1573</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="T23" t="n">
         <v>-0.6201</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5372</v>
+        <v>-0.3088</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1088</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-17.1148</v>
+        <v>-16.4174</v>
       </c>
       <c r="E24" t="n">
-        <v>-11.775</v>
+        <v>-11.7748</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.3402</v>
+        <v>-4.6425</v>
       </c>
       <c r="G24" t="n">
         <v>-5.9581</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4213999999999998</v>
+        <v>0.4214000000000002</v>
       </c>
       <c r="I24" t="n">
         <v>-6.379799999999999</v>
@@ -2305,7 +2305,7 @@
         <v>-4.229000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>5.563599999999999</v>
+        <v>5.5636</v>
       </c>
       <c r="M24" t="n">
         <v>-7.2927</v>
@@ -2326,13 +2326,13 @@
         <v>17.4541</v>
       </c>
       <c r="S24" t="n">
-        <v>-10.6351</v>
+        <v>-9.937800000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.2753</v>
+        <v>-3.2752</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.3599</v>
+        <v>-6.6625</v>
       </c>
       <c r="V24" t="n">
         <v>-2.575</v>
